--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484684_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484684_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. MORAGAS AZNAR</t>
+          <t>V. RODRIGUEZ GIL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0782</v>
+        <v>6.9806</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1449</v>
+        <v>6.884</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9333</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5332</v>
+        <v>1.927</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4592</v>
+        <v>1.9143</v>
       </c>
       <c r="I2" t="n">
-        <v>1.074</v>
+        <v>0.0127</v>
       </c>
       <c r="J2" t="n">
-        <v>3.0356</v>
+        <v>2.3074</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9997</v>
+        <v>2.1983</v>
       </c>
       <c r="L2" t="n">
-        <v>2.036</v>
+        <v>0.1091</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.5024</v>
+        <v>-0.3804</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5404</v>
+        <v>-0.284</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.962</v>
+        <v>-0.0964</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.8326</v>
+        <v>-1.0995</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6493</v>
+        <v>1.0995</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1839</v>
+        <v>0.6191</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3975</v>
+        <v>0.6082</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7864</v>
+        <v>0.0109</v>
       </c>
       <c r="V2" t="n">
-        <v>2.5444</v>
+        <v>4.4344</v>
       </c>
       <c r="W2" t="n">
-        <v>2.5444</v>
+        <v>5.0679</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. RODRIGUEZ GIL</t>
+          <t>M. MORAGAS AZNAR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.033</v>
+        <v>5.4927</v>
       </c>
       <c r="E3" t="n">
-        <v>6.7878</v>
+        <v>4.7576</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2452</v>
+        <v>0.7351</v>
       </c>
       <c r="G3" t="n">
-        <v>1.927</v>
+        <v>1.5332</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9143</v>
+        <v>0.4592</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0127</v>
+        <v>1.074</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3074</v>
+        <v>3.0356</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1983</v>
+        <v>0.9997</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1091</v>
+        <v>2.036</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3804</v>
+        <v>-1.5024</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.284</v>
+        <v>-0.5404</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0964</v>
+        <v>-0.962</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0995</v>
+        <v>-1.8326</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0995</v>
+        <v>1.6493</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6716</v>
+        <v>1.5984</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5121</v>
+        <v>1.0102</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1596</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>4.4344</v>
+        <v>2.5444</v>
       </c>
       <c r="W3" t="n">
-        <v>5.0679</v>
+        <v>2.5444</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5052</v>
+        <v>3.2088</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7948</v>
+        <v>1.4242</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7103</v>
+        <v>1.7846</v>
       </c>
       <c r="G4" t="n">
         <v>2.4669</v>
@@ -766,13 +766,13 @@
         <v>1.2828</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6717</v>
+        <v>0.3754</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4012</v>
+        <v>0.0306</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2705</v>
+        <v>0.3448</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALÁN</t>
+          <t>A. PEREZ RIPOLL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8507</v>
+        <v>2.8765</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8507</v>
+        <v>1.7152</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.1613</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8507</v>
+        <v>3.0055</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9752999999999999</v>
+        <v>1.8673</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8753</v>
+        <v>1.1382</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8507</v>
+        <v>2.2379</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9752999999999999</v>
+        <v>1.4522</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8753</v>
+        <v>0.7857</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.4151</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.3525</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.3665</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.0279</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.1659</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. CAMPOS DE BENGOA</t>
+          <t>A. CEJUDO GALÁN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5076</v>
+        <v>2.8507</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7124</v>
+        <v>2.8507</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2048</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4032</v>
+        <v>2.8507</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1227</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5259</v>
+        <v>1.8753</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6121</v>
+        <v>2.8507</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9195</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6925</v>
+        <v>1.8753</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0152</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7968</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2184</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.361</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1666</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5276999999999999</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. PEREZ RIPOLL</t>
+          <t>J. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3869</v>
+        <v>2.3893</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5229</v>
+        <v>2.7674</v>
       </c>
       <c r="F7" t="n">
-        <v>0.864</v>
+        <v>-0.3782</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0055</v>
+        <v>-0.4032</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8673</v>
+        <v>0.1227</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1382</v>
+        <v>-0.5259</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2379</v>
+        <v>1.6121</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4522</v>
+        <v>0.9195</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7857</v>
+        <v>0.6925</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7675999999999999</v>
+        <v>-2.0152</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4151</v>
+        <v>-0.7968</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3525</v>
+        <v>-1.2184</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3665</v>
+        <v>1.2828</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5498</v>
+        <v>1.2828</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3516</v>
+        <v>0.2426</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2202</v>
+        <v>-0.1116</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1314</v>
+        <v>0.3542</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6335</v>
+        <v>1.267</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3115</v>
+        <v>1.267</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9107</v>
+        <v>2.0342</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2596</v>
+        <v>0.5069</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6512</v>
+        <v>1.5273</v>
       </c>
       <c r="G8" t="n">
         <v>0.123</v>
@@ -1078,13 +1078,13 @@
         <v>1.2828</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6881</v>
+        <v>0.8116</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2919</v>
+        <v>0.5392</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3963</v>
+        <v>0.2724</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0414</v>
+        <v>0.5687</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0187</v>
+        <v>-1.4829</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9773</v>
+        <v>2.0516</v>
       </c>
       <c r="G10" t="n">
         <v>-0.146</v>
@@ -1234,13 +1234,13 @@
         <v>0.9163</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1046</v>
+        <v>0.7147</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4223</v>
+        <v>0.1135</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5269</v>
+        <v>0.6012</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7463</v>
+        <v>-0.7085</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2736</v>
+        <v>0.111</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4727</v>
+        <v>-0.8196</v>
       </c>
       <c r="G11" t="n">
         <v>-1.077</v>
@@ -1312,13 +1312,13 @@
         <v>0.3665</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1187</v>
+        <v>0.1565</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3854</v>
+        <v>-0.0007</v>
       </c>
       <c r="U11" t="n">
-        <v>0.504</v>
+        <v>0.1572</v>
       </c>
       <c r="V11" t="n">
         <v>0.945</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8023</v>
+        <v>-0.9744</v>
       </c>
       <c r="E12" t="n">
-        <v>1.2113</v>
+        <v>0.5933</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0136</v>
+        <v>-1.5677</v>
       </c>
       <c r="G12" t="n">
         <v>2.0091</v>
@@ -1390,13 +1390,13 @@
         <v>0.733</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3327</v>
+        <v>0.1606</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7496</v>
+        <v>0.1316</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4169</v>
+        <v>0.029</v>
       </c>
       <c r="V12" t="n">
         <v>-0.945</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.2151</v>
+        <v>-1.1685</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.508</v>
+        <v>-0.4119</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7071</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>0.4695</v>
@@ -1468,13 +1468,13 @@
         <v>0.3665</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1321</v>
+        <v>0.1787</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0181</v>
+        <v>0.1143</v>
       </c>
       <c r="U13" t="n">
-        <v>0.114</v>
+        <v>0.0645</v>
       </c>
       <c r="V13" t="n">
         <v>-1.267</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.826</v>
+        <v>-1.2902</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.319</v>
+        <v>0.2168</v>
       </c>
       <c r="F14" t="n">
         <v>-1.507</v>
@@ -1546,10 +1546,10 @@
         <v>0.9163</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9163</v>
+        <v>-0.3805</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6056</v>
+        <v>-0.0697</v>
       </c>
       <c r="U14" t="n">
         <v>-0.3107</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.9874</v>
+        <v>-2.0555</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.6147</v>
+        <v>-3.8315</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6274</v>
+        <v>1.776</v>
       </c>
       <c r="G15" t="n">
         <v>-1.4816</v>
@@ -1624,13 +1624,13 @@
         <v>1.4661</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5057</v>
+        <v>0.4261</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7526</v>
+        <v>0.0306</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2469</v>
+        <v>0.3955</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6335</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>21.2291</v>
+        <v>21.7797</v>
       </c>
       <c r="E16" t="n">
-        <v>17.12570000000001</v>
+        <v>17.6761</v>
       </c>
       <c r="F16" t="n">
-        <v>4.103499999999999</v>
+        <v>4.1034</v>
       </c>
       <c r="G16" t="n">
         <v>11.3483</v>
@@ -1702,13 +1702,13 @@
         <v>11.9117</v>
       </c>
       <c r="S16" t="n">
-        <v>4.4908</v>
+        <v>5.0412</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8177</v>
+        <v>2.3683</v>
       </c>
       <c r="U16" t="n">
-        <v>2.6733</v>
+        <v>2.673100000000001</v>
       </c>
       <c r="V16" t="n">
         <v>5.3899</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. DIAGNE</t>
+          <t>M. ABAD MOLINER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3771</v>
+        <v>0.2631</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5908</v>
+        <v>-0.2609</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2136</v>
+        <v>0.5241</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1637</v>
+        <v>-0.6465</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.0965</v>
+        <v>-0.7748</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9327</v>
+        <v>0.1282</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3735</v>
+        <v>-0.5977</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7776</v>
+        <v>-0.5977</v>
       </c>
       <c r="L18" t="n">
-        <v>2.1511</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5373</v>
+        <v>-0.0489</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3189</v>
+        <v>-0.1771</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2184</v>
+        <v>0.1282</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5498</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4661</v>
+        <v>0.5498</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6454</v>
+        <v>0.0092</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1335</v>
+        <v>-0.0139</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5119</v>
+        <v>0.0232</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6543</v>
+        <v>1.267</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6543</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. ABAD MOLINER</t>
+          <t>C. CAMAHORT TORRES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2413</v>
+        <v>0.2345</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3571</v>
+        <v>0.3987</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5984</v>
+        <v>-0.1642</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6465</v>
+        <v>-0.3192</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7748</v>
+        <v>-0.2006</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1282</v>
+        <v>-0.1187</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5977</v>
+        <v>0.7569</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5977</v>
+        <v>0.7153</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.0417</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0489</v>
+        <v>-1.0762</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1771</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1282</v>
+        <v>-0.1603</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3665</v>
+        <v>0.9163</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0126</v>
+        <v>-0.3625</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1101</v>
+        <v>-0.3582</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0975</v>
+        <v>-0.0043</v>
       </c>
       <c r="V19" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. CAMAHORT TORRES</t>
+          <t>M. PERAL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1603</v>
+        <v>-0.3917</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2064</v>
+        <v>0.8253</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3668</v>
+        <v>-1.217</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3192</v>
+        <v>-0.6929</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2006</v>
+        <v>-2.3151</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1187</v>
+        <v>1.6221</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7569</v>
+        <v>1.6519</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7153</v>
+        <v>-0.4834</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0417</v>
+        <v>2.1352</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0762</v>
+        <v>-2.3448</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-1.8317</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1603</v>
+        <v>-0.5131</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9163</v>
+        <v>0.1833</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9163</v>
+        <v>1.0995</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7574</v>
+        <v>0.118</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5505</v>
+        <v>0.0898</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2069</v>
+        <v>0.0283</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. PERAL</t>
+          <t>L. ORSINO BARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5112</v>
+        <v>-0.4649</v>
       </c>
       <c r="E21" t="n">
-        <v>1.21</v>
+        <v>0.0519</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7211</v>
+        <v>-0.5168</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6929</v>
+        <v>0.4343</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.3151</v>
+        <v>-2.1241</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6221</v>
+        <v>2.5583</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6519</v>
+        <v>1.6741</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4834</v>
+        <v>-1.0128</v>
       </c>
       <c r="L21" t="n">
-        <v>2.1352</v>
+        <v>2.6868</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.3448</v>
+        <v>-1.2398</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.8317</v>
+        <v>-1.1113</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5131</v>
+        <v>-0.1285</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1833</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0995</v>
+        <v>0.733</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0015</v>
+        <v>0.0051</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4744</v>
+        <v>-0.1116</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4759</v>
+        <v>0.1167</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.1953</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.1267</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. ORSINO BARCIA</t>
+          <t>E. DIAGNE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8044</v>
+        <v>-0.806</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3327</v>
+        <v>0.7254</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4716</v>
+        <v>-1.5313</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4343</v>
+        <v>-1.1637</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.1241</v>
+        <v>-2.0965</v>
       </c>
       <c r="I22" t="n">
-        <v>2.5583</v>
+        <v>0.9327</v>
       </c>
       <c r="J22" t="n">
-        <v>1.6741</v>
+        <v>1.3735</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.0128</v>
+        <v>-0.7776</v>
       </c>
       <c r="L22" t="n">
-        <v>2.6868</v>
+        <v>2.1511</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2398</v>
+        <v>-2.5373</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1113</v>
+        <v>-1.3189</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1285</v>
+        <v>-1.2184</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.0995</v>
+        <v>0.5498</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R22" t="n">
-        <v>0.733</v>
+        <v>1.4661</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3343</v>
+        <v>0.4623</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4962</v>
+        <v>0.2681</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1619</v>
+        <v>0.1942</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1953</v>
+        <v>-0.6543</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1267</v>
+        <v>-0.6543</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. ARIJA DE LA PENA</t>
+          <t>R. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,40 +2203,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2665</v>
+        <v>-1.271</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3428</v>
+        <v>-0.4222</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9237</v>
+        <v>-0.8489</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.8274</v>
+        <v>-1.7908</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8398</v>
+        <v>-0.1881</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.6672</v>
+        <v>-1.6027</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3269</v>
+        <v>-0.1024</v>
       </c>
       <c r="K23" t="n">
-        <v>2</v>
+        <v>1.8206</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.673</v>
+        <v>-1.9231</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.1543</v>
+        <v>-1.6884</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1602</v>
+        <v>-2.0088</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9941</v>
+        <v>0.3204</v>
       </c>
       <c r="P23" t="n">
         <v>0.3665</v>
@@ -2248,28 +2248,28 @@
         <v>1.2828</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0008</v>
+        <v>-1.1137</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.6704</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0745</v>
+        <v>-0.4433</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1953</v>
+        <v>1.267</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3219</v>
+        <v>1.267</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. HOLGADO CUELLAR</t>
+          <t>D. ARIJA DE LA PENA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,40 +2281,40 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.864</v>
+        <v>-1.3612</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6145</v>
+        <v>-0.3428</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2496</v>
+        <v>-1.0184</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.7908</v>
+        <v>-1.8274</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1881</v>
+        <v>0.8398</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.6027</v>
+        <v>-2.6672</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1024</v>
+        <v>0.3269</v>
       </c>
       <c r="K24" t="n">
-        <v>1.8206</v>
+        <v>2</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.9231</v>
+        <v>-1.673</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.6884</v>
+        <v>-2.1543</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.0088</v>
+        <v>-1.1602</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3204</v>
+        <v>-0.9941</v>
       </c>
       <c r="P24" t="n">
         <v>0.3665</v>
@@ -2326,22 +2326,22 @@
         <v>1.2828</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.7067</v>
+        <v>-0.0956</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8627</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.844</v>
+        <v>-0.0202</v>
       </c>
       <c r="V24" t="n">
-        <v>1.267</v>
+        <v>0.1953</v>
       </c>
       <c r="W24" t="n">
-        <v>1.267</v>
+        <v>0.3219</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.1267</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.9823</v>
+        <v>-1.4359</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3281</v>
+        <v>-0.2319</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.6542</v>
+        <v>-1.204</v>
       </c>
       <c r="G25" t="n">
         <v>2.7495</v>
@@ -2404,13 +2404,13 @@
         <v>1.0995</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.4165</v>
+        <v>-0.8701</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7345</v>
+        <v>-0.6384</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.2317</v>
       </c>
       <c r="V25" t="n">
         <v>-0.7498</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.866</v>
+        <v>-4.0728</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.2078</v>
+        <v>-1.5924</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.6582</v>
+        <v>-2.4804</v>
       </c>
       <c r="G26" t="n">
         <v>-1.2942</v>
@@ -2482,13 +2482,13 @@
         <v>0.733</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2053</v>
+        <v>-0.4121</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0536</v>
+        <v>-0.3311</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2588</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="V26" t="n">
         <v>-1.267</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.4868</v>
+        <v>-5.0453</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.7236</v>
+        <v>-1.4351</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.7632</v>
+        <v>-3.6102</v>
       </c>
       <c r="G27" t="n">
         <v>-3.3736</v>
@@ -2560,13 +2560,13 @@
         <v>1.8326</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.2851</v>
+        <v>-0.8437</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.9909</v>
+        <v>-0.7025</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.2942</v>
+        <v>-0.1412</v>
       </c>
       <c r="V27" t="n">
         <v>-2.6606</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-6.5564</v>
+        <v>-6.2461</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.8542</v>
+        <v>-2.4695</v>
       </c>
       <c r="F28" t="n">
-        <v>-3.7023</v>
+        <v>-3.7766</v>
       </c>
       <c r="G28" t="n">
         <v>-4.0741</v>
@@ -2638,13 +2638,13 @@
         <v>0.9163</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.4161</v>
+        <v>-0.1058</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.5143</v>
+        <v>-0.1297</v>
       </c>
       <c r="U28" t="n">
-        <v>0.0983</v>
+        <v>0.0239</v>
       </c>
       <c r="V28" t="n">
         <v>-2.9826</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-21.2293</v>
+        <v>-19.9471</v>
       </c>
       <c r="E29" t="n">
-        <v>-4.103400000000001</v>
+        <v>-4.1033</v>
       </c>
       <c r="F29" t="n">
-        <v>-17.1259</v>
+        <v>-15.8437</v>
       </c>
       <c r="G29" t="n">
         <v>-11.3484</v>
@@ -2707,7 +2707,7 @@
         <v>-5.772</v>
       </c>
       <c r="P29" t="n">
-        <v>0.0002000000000005331</v>
+        <v>0.000200000000000089</v>
       </c>
       <c r="Q29" t="n">
         <v>-11.9118</v>
@@ -2716,13 +2716,13 @@
         <v>11.9117</v>
       </c>
       <c r="S29" t="n">
-        <v>-4.4909</v>
+        <v>-3.2089</v>
       </c>
       <c r="T29" t="n">
-        <v>-2.6731</v>
+        <v>-2.6733</v>
       </c>
       <c r="U29" t="n">
-        <v>-1.8177</v>
+        <v>-0.5355</v>
       </c>
       <c r="V29" t="n">
         <v>-5.3897</v>
